--- a/site/data/downloads/japan.xlsx
+++ b/site/data/downloads/japan.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="물가" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="고용" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="성장" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="유가" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="금리" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="물가" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="고용" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="성장" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="유가" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="금리" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/site/data/downloads/japan.xlsx
+++ b/site/data/downloads/japan.xlsx
@@ -417,13 +417,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D60"/>
+  <dimension ref="A1:D61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1213,6 +1213,24 @@
       </c>
       <c r="C60" t="n">
         <v>1.8</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="C61" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/site/data/downloads/japan.xlsx
+++ b/site/data/downloads/japan.xlsx
@@ -1244,12 +1244,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C60"/>
+  <dimension ref="A1:C61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1857,6 +1857,21 @@
       </c>
       <c r="B60" t="n">
         <v>2.4</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -2732,7 +2747,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D66"/>
+  <dimension ref="A1:D67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3446,6 +3461,16 @@
         <v>2.94</v>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>3.05</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/data/downloads/japan.xlsx
+++ b/site/data/downloads/japan.xlsx
@@ -1249,7 +1249,7 @@
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1867,11 +1867,6 @@
       </c>
       <c r="B61" t="n">
         <v>2.5</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/site/data/downloads/japan.xlsx
+++ b/site/data/downloads/japan.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D61"/>
+  <dimension ref="A1:D62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1230,6 +1230,24 @@
       <c r="D61" t="inlineStr">
         <is>
           <t>2026-09-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="C62" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
@@ -2116,7 +2134,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C60"/>
+  <dimension ref="A1:C62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2729,6 +2747,26 @@
       </c>
       <c r="B60" t="n">
         <v>77.1318</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>88.05329999999999</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>111.8252</v>
       </c>
     </row>
   </sheetData>
